--- a/documentation/Data Dictionary.xlsx
+++ b/documentation/Data Dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stepheaneff/Documents/work/costed-NAPHS/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46773C05-2007-4046-A505-3F96EDB7B826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BF08C4-E040-BA4F-8798-0CCFD5D31ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="100" yWindow="760" windowWidth="29780" windowHeight="16820" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="100" yWindow="760" windowWidth="29780" windowHeight="16820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table information" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="256">
   <si>
     <t>Text</t>
   </si>
@@ -604,9 +604,6 @@
   </si>
   <si>
     <t>Steph Eaneff</t>
-  </si>
-  <si>
-    <t>The data dictionary was last updated on 23 April, 2025</t>
   </si>
   <si>
     <t>Raw Costed NAPHS data</t>
@@ -761,6 +758,54 @@
   </si>
   <si>
     <t>The estimated cost, standardized to USD (2024). Data were first converted into USD based on published exchange rates of of December of the specified year, then inflation-adjusted based on the CPI to USD (2024).</t>
+  </si>
+  <si>
+    <t>24 April, 2025</t>
+  </si>
+  <si>
+    <t>Update coding of Liberia core capacity to correctly reflect core capacity "Medical Countermeasures" instead of IPC</t>
+  </si>
+  <si>
+    <t>Liberia Costed NAPHS</t>
+  </si>
+  <si>
+    <t>Requirement highlights</t>
+  </si>
+  <si>
+    <t>For plots and specific analysis, brief summary statements of specific requirements documented in the file Clean Costed NAPHS data and Raw Costed NAPHS data, interim file created by research team for the purpose of generating figures</t>
+  </si>
+  <si>
+    <t>one row per desired label on a plot</t>
+  </si>
+  <si>
+    <t>Generated by research team</t>
+  </si>
+  <si>
+    <t>The data dictionary was last updated on 25 April, 2025</t>
+  </si>
+  <si>
+    <t>line_item_id</t>
+  </si>
+  <si>
+    <t>Unique ID</t>
+  </si>
+  <si>
+    <t>A unique line-item ID for each country, requirement, activity, and year</t>
+  </si>
+  <si>
+    <t>manually created by research team (SE) during data cleaning</t>
+  </si>
+  <si>
+    <t>Tagged line items</t>
+  </si>
+  <si>
+    <t>25 April, 2025</t>
+  </si>
+  <si>
+    <t>Added unique IDs to each line item in clean dataset, created separate dataset for the purpose of tagging line-items</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
 </sst>
 </file>
@@ -905,7 +950,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -985,7 +1030,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1007,9 +1052,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1022,7 +1064,46 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1042,45 +1123,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1321,42 +1363,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="16"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
+      <c r="A1" s="28"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
     </row>
     <row r="2" spans="1:22" ht="23" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
     </row>
     <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
     </row>
     <row r="4" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
+      <c r="A4" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
     </row>
     <row r="5" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
     </row>
     <row r="6" spans="1:22" ht="17" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
@@ -1365,54 +1407,54 @@
       <c r="D6" s="6"/>
     </row>
     <row r="7" spans="1:22" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
     </row>
     <row r="8" spans="1:22" ht="32.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="12" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
+      <c r="A9" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
     </row>
     <row r="10" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="16" t="s">
         <v>155</v>
       </c>
       <c r="F10" s="2"/>
@@ -1435,7 +1477,7 @@
     </row>
     <row r="11" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="26" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B11" s="26"/>
       <c r="C11" s="26"/>
@@ -1460,19 +1502,19 @@
       <c r="V11" s="2"/>
     </row>
     <row r="12" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>192</v>
-      </c>
-      <c r="C12" s="22" t="s">
+      <c r="A12" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="16" t="s">
         <v>155</v>
       </c>
       <c r="F12" s="2"/>
@@ -1494,19 +1536,19 @@
       <c r="V12" s="2"/>
     </row>
     <row r="13" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="B13" s="24" t="s">
+      <c r="A13" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="C13" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="C13" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="16" t="s">
         <v>155</v>
       </c>
       <c r="F13" s="2"/>
@@ -1528,20 +1570,20 @@
       <c r="V13" s="2"/>
     </row>
     <row r="14" spans="1:22" ht="97" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="B14" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="C14" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="D14" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E14" s="16" t="s">
         <v>215</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>216</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
@@ -1561,12 +1603,22 @@
       <c r="U14" s="2"/>
       <c r="V14" s="2"/>
     </row>
-    <row r="15" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="7"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="2"/>
+    <row r="15" spans="1:22" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>246</v>
+      </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -1585,12 +1637,22 @@
       <c r="U15" s="2"/>
       <c r="V15" s="2"/>
     </row>
-    <row r="16" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="7"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="2"/>
+    <row r="16" spans="1:22" ht="63" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>246</v>
+      </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -3610,7 +3672,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U1003"/>
+  <dimension ref="A1:U1004"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.19921875" customWidth="1"/>
@@ -3628,98 +3690,83 @@
       <c r="D1" s="6"/>
     </row>
     <row r="2" spans="1:21" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
     </row>
     <row r="3" spans="1:21" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="12" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-    </row>
-    <row r="5" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="22" t="s">
+      <c r="A4" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+    </row>
+    <row r="5" spans="1:21" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C6" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D6" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E6" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F6" s="16" t="s">
         <v>186</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
-    </row>
-    <row r="6" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>210</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -3738,23 +3785,23 @@
       <c r="U6" s="2"/>
     </row>
     <row r="7" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="D7" s="27" t="s">
+      <c r="B7" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="D7" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F7" s="22" t="s">
-        <v>186</v>
+      <c r="F7" s="24" t="s">
+        <v>209</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -3773,22 +3820,22 @@
       <c r="U7" s="2"/>
     </row>
     <row r="8" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="E8" s="22" t="s">
+      <c r="B8" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G8" s="2"/>
@@ -3808,22 +3855,22 @@
       <c r="U8" s="2"/>
     </row>
     <row r="9" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B9" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="E9" s="22" t="s">
+      <c r="B9" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="E9" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G9" s="2"/>
@@ -3843,22 +3890,22 @@
       <c r="U9" s="2"/>
     </row>
     <row r="10" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B10" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="F10" s="22" t="s">
+      <c r="B10" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F10" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G10" s="2"/>
@@ -3878,22 +3925,22 @@
       <c r="U10" s="2"/>
     </row>
     <row r="11" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B11" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="E11" s="22" t="s">
+      <c r="B11" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="E11" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G11" s="2"/>
@@ -3913,22 +3960,22 @@
       <c r="U11" s="2"/>
     </row>
     <row r="12" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B12" s="25" t="s">
-        <v>234</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="D12" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="F12" s="22" t="s">
+      <c r="B12" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="F12" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G12" s="2"/>
@@ -3948,22 +3995,22 @@
       <c r="U12" s="2"/>
     </row>
     <row r="13" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B13" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>237</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="F13" s="22" t="s">
+      <c r="B13" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F13" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G13" s="2"/>
@@ -3982,24 +4029,24 @@
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
     </row>
-    <row r="14" spans="1:21" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="22" t="s">
+    <row r="14" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B14" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>239</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="F14" s="22" t="s">
+      <c r="B14" s="19" t="s">
         <v>216</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>186</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -4017,24 +4064,24 @@
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
     </row>
-    <row r="15" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="22" t="s">
+    <row r="15" spans="1:21" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>164</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>186</v>
+      <c r="B15" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>215</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -4052,68 +4099,68 @@
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
     </row>
-    <row r="16" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-    </row>
-    <row r="17" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="B17" s="22" t="s">
+    <row r="16" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+    </row>
+    <row r="17" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+    </row>
+    <row r="18" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B18" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C18" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D18" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="E17" s="22" t="s">
+      <c r="E18" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F17" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-    </row>
-    <row r="18" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="D18" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="F18" s="22" t="s">
+      <c r="F18" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G18" s="2"/>
@@ -4133,22 +4180,22 @@
       <c r="U18" s="2"/>
     </row>
     <row r="19" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="B19" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="D19" s="27" t="s">
-        <v>167</v>
-      </c>
-      <c r="E19" s="22" t="s">
+      <c r="A19" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="E19" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F19" s="22" t="s">
+      <c r="F19" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G19" s="2"/>
@@ -4168,22 +4215,22 @@
       <c r="U19" s="2"/>
     </row>
     <row r="20" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="C20" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>168</v>
-      </c>
-      <c r="E20" s="22" t="s">
+      <c r="A20" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="E20" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G20" s="2"/>
@@ -4203,22 +4250,22 @@
       <c r="U20" s="2"/>
     </row>
     <row r="21" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="C21" s="22" t="s">
-        <v>160</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="F21" s="22" t="s">
+      <c r="A21" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F21" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G21" s="2"/>
@@ -4238,22 +4285,22 @@
       <c r="U21" s="2"/>
     </row>
     <row r="22" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="B22" s="25" t="s">
-        <v>179</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="E22" s="22" t="s">
+      <c r="A22" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="E22" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G22" s="2"/>
@@ -4273,22 +4320,22 @@
       <c r="U22" s="2"/>
     </row>
     <row r="23" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="B23" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="F23" s="22" t="s">
+      <c r="A23" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="F23" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G23" s="2"/>
@@ -4308,22 +4355,22 @@
       <c r="U23" s="2"/>
     </row>
     <row r="24" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>181</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>163</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>172</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="F24" s="22" t="s">
+      <c r="A24" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F24" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G24" s="2"/>
@@ -4343,22 +4390,22 @@
       <c r="U24" s="2"/>
     </row>
     <row r="25" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>164</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="E25" s="22" t="s">
+      <c r="A25" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="E25" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F25" s="22" t="s">
+      <c r="F25" s="16" t="s">
         <v>186</v>
       </c>
       <c r="G25" s="2"/>
@@ -4378,23 +4425,23 @@
       <c r="U25" s="2"/>
     </row>
     <row r="26" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="B26" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="C26" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="D26" s="29" t="s">
-        <v>204</v>
-      </c>
-      <c r="E26" s="22" t="s">
+      <c r="A26" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="E26" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F26" s="29" t="s">
-        <v>207</v>
+      <c r="F26" s="16" t="s">
+        <v>186</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -4413,23 +4460,23 @@
       <c r="U26" s="2"/>
     </row>
     <row r="27" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B27" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="B27" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="D27" s="29" t="s">
-        <v>205</v>
-      </c>
-      <c r="E27" s="22" t="s">
+      <c r="C27" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="E27" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F27" s="29" t="s">
-        <v>207</v>
+      <c r="F27" s="21" t="s">
+        <v>206</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -4448,23 +4495,23 @@
       <c r="U27" s="2"/>
     </row>
     <row r="28" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="B28" s="22" t="s">
+      <c r="A28" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="C28" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="C28" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="D28" s="29" t="s">
+      <c r="D28" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F28" s="21" t="s">
         <v>206</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="F28" s="29" t="s">
-        <v>207</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
@@ -4482,24 +4529,24 @@
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
     </row>
-    <row r="29" spans="1:21" ht="84" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="B29" s="22" t="s">
-        <v>217</v>
-      </c>
-      <c r="C29" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="D29" s="29" t="s">
-        <v>227</v>
-      </c>
-      <c r="E29" s="22" t="s">
+    <row r="29" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="E29" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F29" s="22" t="s">
-        <v>216</v>
+      <c r="F29" s="21" t="s">
+        <v>206</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -4517,24 +4564,24 @@
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
     </row>
-    <row r="30" spans="1:21" ht="82" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="B30" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="C30" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>228</v>
-      </c>
-      <c r="E30" s="22" t="s">
+    <row r="30" spans="1:21" ht="84" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="E30" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F30" s="22" t="s">
-        <v>216</v>
+      <c r="F30" s="16" t="s">
+        <v>215</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -4553,23 +4600,23 @@
       <c r="U30" s="2"/>
     </row>
     <row r="31" spans="1:21" ht="82" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="B31" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="C31" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>229</v>
-      </c>
-      <c r="E31" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="F31" s="22" t="s">
-        <v>216</v>
+      <c r="A31" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>215</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
@@ -4587,24 +4634,24 @@
       <c r="T31" s="2"/>
       <c r="U31" s="2"/>
     </row>
-    <row r="32" spans="1:21" ht="83" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="C32" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="D32" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="F32" s="22" t="s">
-        <v>216</v>
+    <row r="32" spans="1:21" ht="82" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>215</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -4623,23 +4670,23 @@
       <c r="U32" s="2"/>
     </row>
     <row r="33" spans="1:21" ht="83" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="B33" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>226</v>
-      </c>
-      <c r="D33" s="22" t="s">
-        <v>231</v>
-      </c>
-      <c r="E33" s="22" t="s">
+      <c r="A33" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="E33" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="F33" s="22" t="s">
-        <v>216</v>
+      <c r="F33" s="16" t="s">
+        <v>215</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -4657,13 +4704,25 @@
       <c r="T33" s="2"/>
       <c r="U33" s="2"/>
     </row>
-    <row r="34" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
+    <row r="34" spans="1:21" ht="83" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>215</v>
+      </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -4681,12 +4740,12 @@
       <c r="U34" s="2"/>
     </row>
     <row r="35" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -4704,35 +4763,35 @@
       <c r="U35" s="2"/>
     </row>
     <row r="36" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="11"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3"/>
-      <c r="O36" s="3"/>
-      <c r="P36" s="3"/>
-      <c r="Q36" s="3"/>
-      <c r="R36" s="3"/>
-      <c r="S36" s="3"/>
-      <c r="T36" s="3"/>
-      <c r="U36" s="3"/>
+      <c r="A36" s="10"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
     </row>
     <row r="37" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="11"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
+      <c r="A37" s="10"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -4750,12 +4809,12 @@
       <c r="U37" s="3"/>
     </row>
     <row r="38" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="11"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
+      <c r="A38" s="10"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
@@ -4773,12 +4832,12 @@
       <c r="U38" s="3"/>
     </row>
     <row r="39" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="11"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
+      <c r="A39" s="10"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -4796,12 +4855,12 @@
       <c r="U39" s="3"/>
     </row>
     <row r="40" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="11"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
+      <c r="A40" s="10"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
@@ -4819,12 +4878,12 @@
       <c r="U40" s="3"/>
     </row>
     <row r="41" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="21"/>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
+      <c r="A41" s="10"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -4842,12 +4901,12 @@
       <c r="U41" s="3"/>
     </row>
     <row r="42" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="21"/>
-      <c r="B42" s="21"/>
-      <c r="C42" s="21"/>
-      <c r="D42" s="21"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="21"/>
+      <c r="A42" s="13"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
@@ -4865,12 +4924,12 @@
       <c r="U42" s="3"/>
     </row>
     <row r="43" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
+      <c r="A43" s="13"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
@@ -5140,7 +5199,7 @@
       <c r="T54" s="3"/>
       <c r="U54" s="3"/>
     </row>
-    <row r="55" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -5186,7 +5245,29 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
     </row>
-    <row r="57" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3"/>
+      <c r="P57" s="3"/>
+      <c r="Q57" s="3"/>
+      <c r="R57" s="3"/>
+      <c r="S57" s="3"/>
+      <c r="T57" s="3"/>
+      <c r="U57" s="3"/>
+    </row>
     <row r="58" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="59" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="60" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -6133,11 +6214,12 @@
     <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1002" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1003" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1004" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A17:F17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
@@ -6165,38 +6247,38 @@
       <c r="B1" s="6"/>
     </row>
     <row r="2" spans="1:19" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
     </row>
     <row r="3" spans="1:19" ht="38" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
@@ -8196,43 +8278,45 @@
       <c r="B1" s="6"/>
     </row>
     <row r="2" spans="1:19" ht="37" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
     </row>
     <row r="3" spans="1:19" ht="38" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="15" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="B4" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23" t="s">
+      <c r="B4" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="17" t="s">
+        <v>255</v>
+      </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -8249,18 +8333,18 @@
       <c r="S4" s="2"/>
     </row>
     <row r="5" spans="1:19" ht="118" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="32" t="s">
-        <v>191</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>232</v>
-      </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="23" t="s">
+      <c r="A5" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C5" s="23"/>
+      <c r="D5" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="E5" s="23" t="s">
-        <v>216</v>
+      <c r="E5" s="17" t="s">
+        <v>215</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -8278,11 +8362,19 @@
       <c r="S5" s="2"/>
     </row>
     <row r="6" spans="1:19" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="A6" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="C6" s="23"/>
+      <c r="D6" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>242</v>
+      </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -8299,11 +8391,19 @@
       <c r="S6" s="2"/>
     </row>
     <row r="7" spans="1:19" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="C7" s="23"/>
+      <c r="D7" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>255</v>
+      </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
